--- a/Employee_Reports_wi52/Justine Tiangson Clave Q0590.xlsx
+++ b/Employee_Reports_wi52/Justine Tiangson Clave Q0590.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1265,11 +1265,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-168</v>
+        <v>-176</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1351,11 +1351,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1400,11 +1400,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1501,78 +1501,78 @@
       <c r="K22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="H23" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="H24" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1597,11 +1597,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
